--- a/static/zhijia/新版出口报关单样板.xlsx
+++ b/static/zhijia/新版出口报关单样板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haoya/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D084ABA6-0AD1-7743-B0E8-1AC75D7D0CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A30B61-8101-C542-A58C-955772DEB824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" xr2:uid="{91E24076-8A2C-D340-8D6B-5320156D6ECD}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19800" xr2:uid="{91E24076-8A2C-D340-8D6B-5320156D6ECD}"/>
   </bookViews>
   <sheets>
     <sheet name="出口报关单" sheetId="5" r:id="rId1"/>
@@ -570,121 +570,121 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -966,7 +966,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="7.5" customWidth="1"/>
@@ -984,1383 +984,1382 @@
     <col min="13" max="32" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.25" customHeight="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:14" ht="38.25" customHeight="1">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12" ht="21" customHeight="1">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+    </row>
+    <row r="2" spans="1:14" ht="21" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" ht="60.75" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+    </row>
+    <row r="3" spans="1:14" ht="60.75" customHeight="1">
+      <c r="A3" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="6" t="s">
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="5" t="s">
+      <c r="E3" s="22"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5" t="s">
+      <c r="H3" s="20"/>
+      <c r="I3" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5" t="s">
+      <c r="J3" s="20"/>
+      <c r="K3" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="5"/>
-    </row>
-    <row r="4" spans="1:12" ht="57.75" customHeight="1">
-      <c r="A4" s="9" t="s">
+      <c r="L3" s="20"/>
+    </row>
+    <row r="4" spans="1:14" ht="57.75" customHeight="1">
+      <c r="A4" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="6" t="s">
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="5" t="s">
+      <c r="E4" s="22"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="11" t="s">
+      <c r="H4" s="20"/>
+      <c r="I4" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="13"/>
-    </row>
-    <row r="5" spans="1:12" ht="60" customHeight="1">
-      <c r="A5" s="14" t="s">
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="32"/>
+    </row>
+    <row r="5" spans="1:14" ht="60" customHeight="1">
+      <c r="A5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="6" t="s">
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="14" t="s">
+      <c r="E5" s="22"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5" t="s">
+      <c r="H5" s="20"/>
+      <c r="I5" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-    </row>
-    <row r="6" spans="1:12" ht="54" customHeight="1">
-      <c r="A6" s="15" t="s">
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+    </row>
+    <row r="6" spans="1:14" ht="54" customHeight="1">
+      <c r="A6" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17" t="s">
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="5" t="s">
+      <c r="E6" s="35"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5" t="s">
+      <c r="H6" s="20"/>
+      <c r="I6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5" t="s">
+      <c r="J6" s="20"/>
+      <c r="K6" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="5"/>
-    </row>
-    <row r="7" spans="1:12" ht="31.5" customHeight="1">
-      <c r="A7" s="15" t="s">
+      <c r="L6" s="20"/>
+    </row>
+    <row r="7" spans="1:14" ht="31.5" customHeight="1">
+      <c r="A7" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="20" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="21"/>
-      <c r="F7" s="22" t="s">
+      <c r="E7" s="27"/>
+      <c r="F7" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G7" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="I7" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="J7" s="24" t="s">
+      <c r="J7" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="L7" s="5"/>
-    </row>
-    <row r="8" spans="1:12" ht="38.25" customHeight="1">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-    </row>
-    <row r="9" spans="1:12" ht="52.5" customHeight="1">
-      <c r="A9" s="14" t="s">
+      <c r="L7" s="20"/>
+    </row>
+    <row r="8" spans="1:14" ht="38.25" customHeight="1">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+    </row>
+    <row r="9" spans="1:14" ht="52.5" customHeight="1">
+      <c r="A9" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-    </row>
-    <row r="10" spans="1:12" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A10" s="22" t="s">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+    </row>
+    <row r="10" spans="1:14" ht="34.5" customHeight="1" thickBot="1">
+      <c r="A10" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="30" t="s">
+      <c r="F10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="I10" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="22" t="s">
+      <c r="J10" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="K10" s="22" t="s">
+      <c r="K10" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="24" t="s">
+      <c r="L10" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="20">
-      <c r="A11" s="31">
+    <row r="11" spans="1:14" ht="20">
+      <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="33" t="s">
+      <c r="B11" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="34">
-        <v>400</v>
-      </c>
-      <c r="E11" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="35">
+      <c r="D11" s="11">
+        <v>400</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="12">
         <f t="shared" ref="F11:F23" si="0">G11/D11</f>
         <v>2.9166660000000002</v>
       </c>
-      <c r="G11" s="34">
+      <c r="G11" s="11">
         <v>1166.6664000000001</v>
       </c>
-      <c r="H11" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I11" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K11" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L11" s="37"/>
-    </row>
-    <row r="12" spans="1:12" ht="20">
-      <c r="A12" s="31">
+      <c r="H11" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L11" s="14"/>
+      <c r="N11" s="39"/>
+    </row>
+    <row r="12" spans="1:14" ht="20">
+      <c r="A12" s="8">
         <v>2</v>
       </c>
-      <c r="B12" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="38" t="s">
+      <c r="B12" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="34">
-        <v>400</v>
-      </c>
-      <c r="E12" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="35">
+      <c r="D12" s="11">
+        <v>400</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="12">
         <f t="shared" si="0"/>
         <v>2.4166660000000002</v>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="11">
         <v>966.66640000000007</v>
       </c>
-      <c r="H12" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I12" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J12" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K12" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L12" s="37"/>
-    </row>
-    <row r="13" spans="1:12" ht="20">
-      <c r="A13" s="31">
+      <c r="H12" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L12" s="14"/>
+    </row>
+    <row r="13" spans="1:14" ht="20">
+      <c r="A13" s="8">
         <v>3</v>
       </c>
-      <c r="B13" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="38" t="s">
+      <c r="B13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="11">
         <v>200</v>
       </c>
-      <c r="E13" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="35">
+      <c r="E13" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="12">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="11">
         <v>500</v>
       </c>
-      <c r="H13" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I13" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J13" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K13" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L13" s="37"/>
-    </row>
-    <row r="14" spans="1:12" ht="20">
-      <c r="A14" s="31">
+      <c r="H13" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L13" s="14"/>
+    </row>
+    <row r="14" spans="1:14" ht="20">
+      <c r="A14" s="8">
         <v>4</v>
       </c>
-      <c r="B14" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="38" t="s">
+      <c r="B14" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="11">
         <v>200</v>
       </c>
-      <c r="E14" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="35">
+      <c r="E14" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="12">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="11">
         <v>500</v>
       </c>
-      <c r="H14" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I14" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J14" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K14" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L14" s="37"/>
-    </row>
-    <row r="15" spans="1:12" ht="20">
-      <c r="A15" s="31">
+      <c r="H14" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L14" s="14"/>
+    </row>
+    <row r="15" spans="1:14" ht="20">
+      <c r="A15" s="8">
         <v>5</v>
       </c>
-      <c r="B15" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="38" t="s">
+      <c r="B15" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="34">
-        <v>400</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="35">
+      <c r="D15" s="11">
+        <v>400</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="12">
         <f t="shared" si="0"/>
         <v>2.4166660000000002</v>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="11">
         <v>966.66640000000007</v>
       </c>
-      <c r="H15" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I15" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K15" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L15" s="37"/>
-    </row>
-    <row r="16" spans="1:12" ht="20">
-      <c r="A16" s="31">
+      <c r="H15" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L15" s="14"/>
+    </row>
+    <row r="16" spans="1:14" ht="20">
+      <c r="A16" s="8">
         <v>6</v>
       </c>
-      <c r="B16" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="38" t="s">
+      <c r="B16" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="34">
-        <v>400</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="35">
+      <c r="D16" s="11">
+        <v>400</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="12">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="G16" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H16" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I16" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J16" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K16" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L16" s="37"/>
+      <c r="G16" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L16" s="14"/>
     </row>
     <row r="17" spans="1:12" ht="20">
-      <c r="A17" s="31">
+      <c r="A17" s="8">
         <v>7</v>
       </c>
-      <c r="B17" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="38" t="s">
+      <c r="B17" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="34">
-        <v>400</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="35">
+      <c r="D17" s="11">
+        <v>400</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="12">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="G17" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H17" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I17" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J17" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K17" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L17" s="37"/>
+      <c r="G17" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L17" s="14"/>
     </row>
     <row r="18" spans="1:12" ht="20">
-      <c r="A18" s="31">
+      <c r="A18" s="8">
         <v>8</v>
       </c>
-      <c r="B18" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="38" t="s">
+      <c r="B18" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="34">
-        <v>400</v>
-      </c>
-      <c r="E18" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="35">
+      <c r="D18" s="11">
+        <v>400</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="12">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="G18" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H18" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I18" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J18" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K18" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L18" s="37"/>
+      <c r="G18" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L18" s="14"/>
     </row>
     <row r="19" spans="1:12" ht="20">
-      <c r="A19" s="31">
+      <c r="A19" s="8">
         <v>9</v>
       </c>
-      <c r="B19" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="38" t="s">
+      <c r="B19" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="34">
-        <v>400</v>
-      </c>
-      <c r="E19" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="35">
+      <c r="D19" s="11">
+        <v>400</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="12">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="G19" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H19" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I19" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J19" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K19" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L19" s="37"/>
+      <c r="G19" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L19" s="14"/>
     </row>
     <row r="20" spans="1:12" ht="20">
-      <c r="A20" s="31">
+      <c r="A20" s="8">
         <v>10</v>
       </c>
-      <c r="B20" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="38" t="s">
+      <c r="B20" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="34">
-        <v>400</v>
-      </c>
-      <c r="E20" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="35">
+      <c r="D20" s="11">
+        <v>400</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="12">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="G20" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H20" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I20" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J20" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K20" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L20" s="37"/>
+      <c r="G20" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L20" s="14"/>
     </row>
     <row r="21" spans="1:12" ht="20">
-      <c r="A21" s="31">
+      <c r="A21" s="8">
         <v>11</v>
       </c>
-      <c r="B21" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="38" t="s">
+      <c r="B21" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="34">
-        <v>400</v>
-      </c>
-      <c r="E21" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="35">
+      <c r="D21" s="11">
+        <v>400</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="12">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="G21" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H21" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I21" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J21" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K21" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L21" s="37"/>
+      <c r="G21" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L21" s="14"/>
     </row>
     <row r="22" spans="1:12" ht="20">
-      <c r="A22" s="31">
+      <c r="A22" s="8">
         <v>12</v>
       </c>
-      <c r="B22" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="38" t="s">
+      <c r="B22" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="34">
-        <v>400</v>
-      </c>
-      <c r="E22" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" s="35">
+      <c r="D22" s="11">
+        <v>400</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="12">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="G22" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H22" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I22" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J22" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K22" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L22" s="37"/>
+      <c r="G22" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L22" s="14"/>
     </row>
     <row r="23" spans="1:12" ht="20">
-      <c r="A23" s="31">
+      <c r="A23" s="8">
         <v>13</v>
       </c>
-      <c r="B23" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="38" t="s">
+      <c r="B23" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D23" s="34">
-        <v>400</v>
-      </c>
-      <c r="E23" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="35">
+      <c r="D23" s="11">
+        <v>400</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" s="12">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="G23" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H23" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I23" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J23" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K23" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L23" s="37"/>
+      <c r="G23" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L23" s="14"/>
     </row>
     <row r="24" spans="1:12" ht="20">
-      <c r="A24" s="31">
+      <c r="A24" s="8">
         <v>14</v>
       </c>
-      <c r="B24" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="38" t="s">
+      <c r="B24" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="34">
-        <v>400</v>
-      </c>
-      <c r="E24" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="35">
+      <c r="D24" s="11">
+        <v>400</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="12">
         <f t="shared" ref="F24:F40" si="1">G24/D24</f>
         <v>2.5</v>
       </c>
-      <c r="G24" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H24" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I24" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J24" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K24" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L24" s="37"/>
+      <c r="G24" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L24" s="14"/>
     </row>
     <row r="25" spans="1:12" ht="20">
-      <c r="A25" s="31">
+      <c r="A25" s="8">
         <v>15</v>
       </c>
-      <c r="B25" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="38" t="s">
+      <c r="B25" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D25" s="34">
-        <v>400</v>
-      </c>
-      <c r="E25" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F25" s="35">
+      <c r="D25" s="11">
+        <v>400</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" s="12">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="G25" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H25" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I25" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J25" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K25" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L25" s="37"/>
+      <c r="G25" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L25" s="14"/>
     </row>
     <row r="26" spans="1:12" ht="20">
-      <c r="A26" s="31">
+      <c r="A26" s="8">
         <v>16</v>
       </c>
-      <c r="B26" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="38" t="s">
+      <c r="B26" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="34">
-        <v>400</v>
-      </c>
-      <c r="E26" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F26" s="35">
+      <c r="D26" s="11">
+        <v>400</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" s="12">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="G26" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H26" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I26" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J26" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K26" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L26" s="37"/>
+      <c r="G26" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L26" s="14"/>
     </row>
     <row r="27" spans="1:12" ht="20">
-      <c r="A27" s="31">
+      <c r="A27" s="8">
         <v>17</v>
       </c>
-      <c r="B27" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="38" t="s">
+      <c r="B27" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="34">
-        <v>400</v>
-      </c>
-      <c r="E27" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F27" s="35">
+      <c r="D27" s="11">
+        <v>400</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="12">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="G27" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H27" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I27" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J27" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K27" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L27" s="37"/>
+      <c r="G27" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L27" s="14"/>
     </row>
     <row r="28" spans="1:12" ht="20">
-      <c r="A28" s="31">
+      <c r="A28" s="8">
         <v>18</v>
       </c>
-      <c r="B28" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" s="38" t="s">
+      <c r="B28" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="34">
-        <v>400</v>
-      </c>
-      <c r="E28" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F28" s="35">
+      <c r="D28" s="11">
+        <v>400</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="12">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="G28" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H28" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I28" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J28" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K28" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L28" s="37"/>
+      <c r="G28" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L28" s="14"/>
     </row>
     <row r="29" spans="1:12" ht="20">
-      <c r="A29" s="31">
+      <c r="A29" s="8">
         <v>19</v>
       </c>
-      <c r="B29" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="38" t="s">
+      <c r="B29" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="34">
-        <v>400</v>
-      </c>
-      <c r="E29" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F29" s="35">
+      <c r="D29" s="11">
+        <v>400</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F29" s="12">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="G29" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H29" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I29" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J29" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K29" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L29" s="37"/>
+      <c r="G29" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L29" s="14"/>
     </row>
     <row r="30" spans="1:12" ht="20">
-      <c r="A30" s="31">
+      <c r="A30" s="8">
         <v>20</v>
       </c>
-      <c r="B30" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="38" t="s">
+      <c r="B30" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="D30" s="34">
-        <v>400</v>
-      </c>
-      <c r="E30" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F30" s="35">
+      <c r="D30" s="11">
+        <v>400</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="12">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="G30" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H30" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I30" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J30" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K30" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L30" s="37"/>
+      <c r="G30" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K30" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L30" s="14"/>
     </row>
     <row r="31" spans="1:12" ht="20">
-      <c r="A31" s="31">
+      <c r="A31" s="8">
         <v>21</v>
       </c>
-      <c r="B31" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" s="38" t="s">
+      <c r="B31" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="34">
-        <v>400</v>
-      </c>
-      <c r="E31" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F31" s="35">
+      <c r="D31" s="11">
+        <v>400</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F31" s="12">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="G31" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H31" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I31" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J31" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K31" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L31" s="37"/>
+      <c r="G31" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K31" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L31" s="14"/>
     </row>
     <row r="32" spans="1:12" ht="20">
-      <c r="A32" s="31">
+      <c r="A32" s="8">
         <v>22</v>
       </c>
-      <c r="B32" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" s="38" t="s">
+      <c r="B32" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="34">
-        <v>400</v>
-      </c>
-      <c r="E32" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F32" s="35">
+      <c r="D32" s="11">
+        <v>400</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F32" s="12">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="G32" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H32" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I32" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J32" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K32" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L32" s="37"/>
+      <c r="G32" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K32" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L32" s="14"/>
     </row>
     <row r="33" spans="1:12" ht="20">
-      <c r="A33" s="31">
+      <c r="A33" s="8">
         <v>23</v>
       </c>
-      <c r="B33" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" s="38" t="s">
+      <c r="B33" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="D33" s="34">
-        <v>400</v>
-      </c>
-      <c r="E33" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F33" s="35">
+      <c r="D33" s="11">
+        <v>400</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" s="12">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="G33" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H33" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I33" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J33" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K33" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L33" s="37"/>
+      <c r="G33" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J33" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K33" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L33" s="14"/>
     </row>
     <row r="34" spans="1:12" ht="20">
-      <c r="A34" s="31">
+      <c r="A34" s="8">
         <v>24</v>
       </c>
-      <c r="B34" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C34" s="38" t="s">
+      <c r="B34" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="D34" s="34">
-        <v>400</v>
-      </c>
-      <c r="E34" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F34" s="35">
+      <c r="D34" s="11">
+        <v>400</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F34" s="12">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="G34" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H34" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I34" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J34" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K34" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L34" s="37"/>
+      <c r="G34" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L34" s="14"/>
     </row>
     <row r="35" spans="1:12" ht="20">
-      <c r="A35" s="31">
+      <c r="A35" s="8">
         <v>25</v>
       </c>
-      <c r="B35" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C35" s="38" t="s">
+      <c r="B35" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="D35" s="34">
-        <v>400</v>
-      </c>
-      <c r="E35" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F35" s="35">
+      <c r="D35" s="11">
+        <v>400</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F35" s="12">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="G35" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H35" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I35" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J35" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K35" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L35" s="37"/>
+      <c r="G35" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K35" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L35" s="14"/>
     </row>
     <row r="36" spans="1:12" ht="20">
-      <c r="A36" s="31">
+      <c r="A36" s="8">
         <v>26</v>
       </c>
-      <c r="B36" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" s="38" t="s">
+      <c r="B36" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="D36" s="34">
-        <v>400</v>
-      </c>
-      <c r="E36" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F36" s="35">
+      <c r="D36" s="11">
+        <v>400</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F36" s="12">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="G36" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H36" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I36" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J36" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K36" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L36" s="37"/>
+      <c r="G36" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K36" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L36" s="14"/>
     </row>
     <row r="37" spans="1:12" ht="20">
-      <c r="A37" s="31">
-        <v>27</v>
-      </c>
-      <c r="B37" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C37" s="38" t="s">
+      <c r="A37" s="8">
+        <v>27</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D37" s="34">
-        <v>400</v>
-      </c>
-      <c r="E37" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F37" s="35">
+      <c r="D37" s="11">
+        <v>400</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F37" s="12">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="G37" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H37" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I37" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J37" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K37" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L37" s="37"/>
+      <c r="G37" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K37" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L37" s="14"/>
     </row>
     <row r="38" spans="1:12" ht="20">
-      <c r="A38" s="31">
-        <v>28</v>
-      </c>
-      <c r="B38" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C38" s="38" t="s">
+      <c r="A38" s="8">
+        <v>28</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D38" s="34">
-        <v>400</v>
-      </c>
-      <c r="E38" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F38" s="35">
+      <c r="D38" s="11">
+        <v>400</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" s="12">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="G38" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H38" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I38" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J38" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K38" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L38" s="37"/>
+      <c r="G38" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I38" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K38" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L38" s="14"/>
     </row>
     <row r="39" spans="1:12" ht="20">
-      <c r="A39" s="31">
-        <v>29</v>
-      </c>
-      <c r="B39" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C39" s="38" t="s">
+      <c r="A39" s="8">
+        <v>29</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D39" s="34">
-        <v>400</v>
-      </c>
-      <c r="E39" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F39" s="35">
+      <c r="D39" s="11">
+        <v>400</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F39" s="12">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="G39" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H39" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I39" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J39" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K39" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L39" s="37"/>
+      <c r="G39" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K39" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L39" s="14"/>
     </row>
     <row r="40" spans="1:12" ht="21" thickBot="1">
-      <c r="A40" s="31">
-        <v>30</v>
-      </c>
-      <c r="B40" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C40" s="39" t="s">
+      <c r="A40" s="8">
+        <v>30</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D40" s="34">
-        <v>400</v>
-      </c>
-      <c r="E40" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F40" s="35">
+      <c r="D40" s="11">
+        <v>400</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="12">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="G40" s="34">
-        <v>1000</v>
-      </c>
-      <c r="H40" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="I40" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="J40" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="K40" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="L40" s="37"/>
+      <c r="G40" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J40" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K40" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L40" s="14"/>
     </row>
     <row r="41" spans="1:12" ht="34.5" customHeight="1">
-      <c r="A41" s="40" t="s">
+      <c r="A41" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="40"/>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="40"/>
-      <c r="F41" s="40"/>
-      <c r="G41" s="40"/>
-      <c r="H41" s="40"/>
-      <c r="I41" s="40"/>
-      <c r="J41" s="40"/>
-      <c r="K41" s="40"/>
-      <c r="L41" s="40"/>
+      <c r="B41" s="38"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="38"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="38"/>
+      <c r="J41" s="38"/>
+      <c r="K41" s="38"/>
+      <c r="L41" s="38"/>
     </row>
     <row r="42" spans="1:12" ht="83.25" customHeight="1">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="14" t="s">
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="L42" s="5"/>
+      <c r="L42" s="20"/>
     </row>
     <row r="44" spans="1:12" ht="18.75" customHeight="1"/>
     <row r="45" spans="1:12" ht="27" customHeight="1"/>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="K42:L42"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="K7:L7"/>
@@ -2377,11 +2376,13 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="K6:L6"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A42:J42"/>
-    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
